--- a/examples/sales.xlsx
+++ b/examples/sales.xlsx
@@ -15,38 +15,25 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,38 +41,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -204,7 +169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -223,6 +188,16 @@
           <t>Price</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -235,8 +210,16 @@
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>1200</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -250,8 +233,16 @@
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>25</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -265,8 +256,85 @@
           <t>Furniture</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>300</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chair</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lamp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
       </c>
     </row>
   </sheetData>
